--- a/astro-site/public/dl/kit-tareas-sushi-bar/03-seguridad-anisakis-appcc.xlsx
+++ b/astro-site/public/dl/kit-tareas-sushi-bar/03-seguridad-anisakis-appcc.xlsx
@@ -12,7 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temperaturas Diario" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad Pescado" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Registro Congelacion'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Temperaturas Diario'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Trazabilidad Pescado'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -521,14 +525,15 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -536,6 +541,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -543,6 +549,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -578,6 +585,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -585,6 +593,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -613,6 +622,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -620,8 +630,25 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-sushi-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -630,7 +657,7 @@
   <sheetPr>
     <tabColor rgb="00D32F2F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -667,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -974,6 +1002,7 @@
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="11" t="inlineStr">
         <is>
@@ -981,6 +1010,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="B29" s="12" t="inlineStr">
         <is>
@@ -990,12 +1020,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B27:I27"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1004,7 +1043,7 @@
   <sheetPr>
     <tabColor rgb="00E65100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1034,6 +1073,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1200,6 +1240,8 @@
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="12" t="inlineStr">
         <is>
@@ -1216,10 +1258,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1228,7 +1279,7 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1250,6 +1301,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
@@ -1536,6 +1588,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>